--- a/Inventario.xlsx
+++ b/Inventario.xlsx
@@ -1,22 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\default.LAPTOP-1S186SIQ\Proyecto\Proyecto inventario\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18022F64-2BDE-4A8C-BE6C-E0621D713E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>PRODUCTOS</t>
   </si>
@@ -33,59 +38,74 @@
     <t>FECHA DE INGRESO</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>pastel</t>
-  </si>
-  <si>
-    <t>Lote</t>
-  </si>
-  <si>
-    <t>225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lote </t>
-  </si>
-  <si>
-    <t>550</t>
-  </si>
-  <si>
-    <t>Inicial</t>
-  </si>
-  <si>
-    <t>300</t>
+    <t>LOTE</t>
+  </si>
+  <si>
+    <t>cortina</t>
+  </si>
+  <si>
+    <t>camera</t>
+  </si>
+  <si>
+    <t>camisa</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>15/3/2026</t>
+  </si>
+  <si>
+    <t>16/3/2026</t>
+  </si>
+  <si>
+    <t>17/3/2026</t>
+  </si>
+  <si>
+    <t>18/3/2026</t>
   </si>
   <si>
     <t>N.1</t>
   </si>
   <si>
-    <t>600</t>
-  </si>
-  <si>
-    <t>13-3-2026</t>
-  </si>
-  <si>
-    <t>13/3/2026</t>
-  </si>
-  <si>
-    <t>productos</t>
-  </si>
-  <si>
-    <t>lotes</t>
-  </si>
-  <si>
-    <t>nombres de los productos</t>
-  </si>
-  <si>
-    <t>cantidades totales de los productos</t>
+    <t>N.2</t>
+  </si>
+  <si>
+    <t>N.3</t>
+  </si>
+  <si>
+    <t>N.4</t>
+  </si>
+  <si>
+    <t>N.5</t>
+  </si>
+  <si>
+    <t>N.6</t>
+  </si>
+  <si>
+    <t>N.7</t>
+  </si>
+  <si>
+    <t>N.8</t>
+  </si>
+  <si>
+    <t>N.9</t>
+  </si>
+  <si>
+    <t>Nombre de los productos</t>
+  </si>
+  <si>
+    <t>Cantidad total de los productos</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -122,13 +142,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -166,7 +194,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -200,6 +228,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -234,9 +263,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -409,11 +439,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.36328125" customWidth="1"/>
+    <col min="2" max="2" width="14.90625" customWidth="1"/>
+    <col min="3" max="4" width="10.36328125" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -429,73 +465,185 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2">
+        <v>150</v>
+      </c>
+      <c r="D2">
+        <v>300</v>
+      </c>
+      <c r="E2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
+      <c r="C3">
+        <v>150</v>
+      </c>
+      <c r="D3">
+        <v>300</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <v>200</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+        <v>12</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>300</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>100</v>
+      </c>
+      <c r="D6">
+        <v>200</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>150</v>
+      </c>
+      <c r="D7">
+        <v>300</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="D8">
+        <v>200</v>
+      </c>
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
         <v>10</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C9">
+        <v>150</v>
+      </c>
+      <c r="D9">
+        <v>300</v>
+      </c>
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
-        <v>16</v>
+      <c r="F10" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -504,50 +652,44 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="27.54296875" customWidth="1"/>
+    <col min="2" max="2" width="29.08984375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
